--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113779</v>
+        <v>125113789</v>
       </c>
       <c r="B2" t="n">
-        <v>79892</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454550</v>
+        <v>454622</v>
       </c>
       <c r="R2" t="n">
-        <v>6991138</v>
+        <v>6991320</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113733</v>
+        <v>125113788</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454545</v>
+        <v>454659</v>
       </c>
       <c r="R3" t="n">
-        <v>6991197</v>
+        <v>6991284</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113737</v>
+        <v>125113787</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454585</v>
+        <v>454637</v>
       </c>
       <c r="R4" t="n">
-        <v>6991218</v>
+        <v>6991264</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113769</v>
+        <v>125113768</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454641</v>
+        <v>454639</v>
       </c>
       <c r="R5" t="n">
-        <v>6991336</v>
+        <v>6991313</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1061,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113774</v>
+        <v>125113763</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1138,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454593</v>
+        <v>454720</v>
       </c>
       <c r="R6" t="n">
-        <v>6991337</v>
+        <v>6991164</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1168,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113767</v>
+        <v>125113766</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1245,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454642</v>
+        <v>454646</v>
       </c>
       <c r="R7" t="n">
-        <v>6991318</v>
+        <v>6991263</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113791</v>
+        <v>125113772</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454558</v>
+        <v>454591</v>
       </c>
       <c r="R8" t="n">
-        <v>6991102</v>
+        <v>6991345</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113762</v>
+        <v>125113793</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454765</v>
+        <v>454627</v>
       </c>
       <c r="R9" t="n">
-        <v>6991225</v>
+        <v>6991135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113788</v>
+        <v>125113783</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454659</v>
+        <v>454548</v>
       </c>
       <c r="R10" t="n">
-        <v>6991284</v>
+        <v>6991137</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113738</v>
+        <v>125113791</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454619</v>
+        <v>454558</v>
       </c>
       <c r="R11" t="n">
-        <v>6991149</v>
+        <v>6991102</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1698,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113732</v>
+        <v>125113762</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1775,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454544</v>
+        <v>454765</v>
       </c>
       <c r="R12" t="n">
-        <v>6991166</v>
+        <v>6991225</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1832,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113736</v>
+        <v>125113741</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1882,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454612</v>
+        <v>454605</v>
       </c>
       <c r="R13" t="n">
-        <v>6991255</v>
+        <v>6991152</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113789</v>
+        <v>125113733</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454622</v>
+        <v>454545</v>
       </c>
       <c r="R14" t="n">
-        <v>6991320</v>
+        <v>6991197</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,6 +2015,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113783</v>
+        <v>125113739</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454548</v>
+        <v>454621</v>
       </c>
       <c r="R15" t="n">
-        <v>6991137</v>
+        <v>6991148</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,6 +2122,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113771</v>
+        <v>125113737</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454604</v>
+        <v>454585</v>
       </c>
       <c r="R16" t="n">
-        <v>6991338</v>
+        <v>6991218</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,7 +2260,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113773</v>
+        <v>125113769</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454593</v>
+        <v>454641</v>
       </c>
       <c r="R17" t="n">
-        <v>6991340</v>
+        <v>6991336</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113770</v>
+        <v>125113735</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454639</v>
+        <v>454573</v>
       </c>
       <c r="R18" t="n">
-        <v>6991344</v>
+        <v>6991262</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,7 +2474,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113768</v>
+        <v>125113764</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454639</v>
+        <v>454623</v>
       </c>
       <c r="R19" t="n">
-        <v>6991313</v>
+        <v>6991163</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113787</v>
+        <v>125113767</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2597,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454637</v>
+        <v>454642</v>
       </c>
       <c r="R20" t="n">
-        <v>6991264</v>
+        <v>6991318</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,6 +2657,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2683,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113743</v>
+        <v>125113745</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2723,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454601</v>
+        <v>454575</v>
       </c>
       <c r="R21" t="n">
-        <v>6991125</v>
+        <v>6991102</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2790,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113741</v>
+        <v>125113736</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2830,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454605</v>
+        <v>454612</v>
       </c>
       <c r="R22" t="n">
-        <v>6991152</v>
+        <v>6991255</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2897,7 +2902,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113739</v>
+        <v>125113743</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454621</v>
+        <v>454601</v>
       </c>
       <c r="R23" t="n">
-        <v>6991148</v>
+        <v>6991125</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,7 +2982,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3004,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113772</v>
+        <v>125113738</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3044,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454591</v>
+        <v>454619</v>
       </c>
       <c r="R24" t="n">
-        <v>6991345</v>
+        <v>6991149</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113766</v>
+        <v>125113779</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3127,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454646</v>
+        <v>454550</v>
       </c>
       <c r="R25" t="n">
-        <v>6991263</v>
+        <v>6991138</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3187,11 +3192,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,7 +3218,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113734</v>
+        <v>125113761</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454580</v>
+        <v>454762</v>
       </c>
       <c r="R26" t="n">
-        <v>6991256</v>
+        <v>6991205</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3325,7 +3325,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113764</v>
+        <v>125113734</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454623</v>
+        <v>454580</v>
       </c>
       <c r="R27" t="n">
-        <v>6991163</v>
+        <v>6991256</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3432,7 +3432,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125113745</v>
+        <v>125113731</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454575</v>
+        <v>454544</v>
       </c>
       <c r="R28" t="n">
-        <v>6991102</v>
+        <v>6991123</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3539,7 +3539,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125113735</v>
+        <v>125113732</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454573</v>
+        <v>454544</v>
       </c>
       <c r="R29" t="n">
-        <v>6991262</v>
+        <v>6991166</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3646,10 +3646,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125113793</v>
+        <v>125113770</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3662,21 +3662,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454627</v>
+        <v>454639</v>
       </c>
       <c r="R30" t="n">
-        <v>6991135</v>
+        <v>6991344</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3753,7 +3753,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125113761</v>
+        <v>125113774</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454762</v>
+        <v>454593</v>
       </c>
       <c r="R31" t="n">
-        <v>6991205</v>
+        <v>6991337</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125113763</v>
+        <v>125113771</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454720</v>
+        <v>454604</v>
       </c>
       <c r="R32" t="n">
-        <v>6991164</v>
+        <v>6991338</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3967,7 +3967,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125113731</v>
+        <v>125113773</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454544</v>
+        <v>454593</v>
       </c>
       <c r="R33" t="n">
-        <v>6991123</v>
+        <v>6991340</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113789</v>
+        <v>125113734</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454622</v>
+        <v>454580</v>
       </c>
       <c r="R2" t="n">
-        <v>6991320</v>
+        <v>6991256</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113788</v>
+        <v>125113743</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454659</v>
+        <v>454601</v>
       </c>
       <c r="R3" t="n">
-        <v>6991284</v>
+        <v>6991125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113787</v>
+        <v>125113764</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454637</v>
+        <v>454623</v>
       </c>
       <c r="R4" t="n">
-        <v>6991264</v>
+        <v>6991163</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113768</v>
+        <v>125113737</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1021,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454639</v>
+        <v>454585</v>
       </c>
       <c r="R5" t="n">
-        <v>6991313</v>
+        <v>6991218</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113763</v>
+        <v>125113771</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1128,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454720</v>
+        <v>454604</v>
       </c>
       <c r="R6" t="n">
-        <v>6991164</v>
+        <v>6991338</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113766</v>
+        <v>125113779</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454646</v>
+        <v>454550</v>
       </c>
       <c r="R7" t="n">
-        <v>6991263</v>
+        <v>6991138</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113772</v>
+        <v>125113770</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1342,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454591</v>
+        <v>454639</v>
       </c>
       <c r="R8" t="n">
-        <v>6991345</v>
+        <v>6991344</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113793</v>
+        <v>125113774</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454627</v>
+        <v>454593</v>
       </c>
       <c r="R9" t="n">
-        <v>6991135</v>
+        <v>6991337</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113783</v>
+        <v>125113732</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454548</v>
+        <v>454544</v>
       </c>
       <c r="R10" t="n">
-        <v>6991137</v>
+        <v>6991166</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113791</v>
+        <v>125113731</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454558</v>
+        <v>454544</v>
       </c>
       <c r="R11" t="n">
-        <v>6991102</v>
+        <v>6991123</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113762</v>
+        <v>125113772</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1765,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454765</v>
+        <v>454591</v>
       </c>
       <c r="R12" t="n">
-        <v>6991225</v>
+        <v>6991345</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1820,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113741</v>
+        <v>125113733</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1872,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454605</v>
+        <v>454545</v>
       </c>
       <c r="R13" t="n">
-        <v>6991152</v>
+        <v>6991197</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1927,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113733</v>
+        <v>125113773</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1979,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454545</v>
+        <v>454593</v>
       </c>
       <c r="R14" t="n">
-        <v>6991197</v>
+        <v>6991340</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113739</v>
+        <v>125113762</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2086,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454621</v>
+        <v>454765</v>
       </c>
       <c r="R15" t="n">
-        <v>6991148</v>
+        <v>6991225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113737</v>
+        <v>125113735</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2193,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454585</v>
+        <v>454573</v>
       </c>
       <c r="R16" t="n">
-        <v>6991218</v>
+        <v>6991262</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113769</v>
+        <v>125113767</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2300,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454641</v>
+        <v>454642</v>
       </c>
       <c r="R17" t="n">
-        <v>6991336</v>
+        <v>6991318</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113735</v>
+        <v>125113791</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454573</v>
+        <v>454558</v>
       </c>
       <c r="R18" t="n">
-        <v>6991262</v>
+        <v>6991102</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2462,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113764</v>
+        <v>125113768</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2514,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454623</v>
+        <v>454639</v>
       </c>
       <c r="R19" t="n">
-        <v>6991163</v>
+        <v>6991313</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2569,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,7 +2596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113767</v>
+        <v>125113736</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2621,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454642</v>
+        <v>454612</v>
       </c>
       <c r="R20" t="n">
-        <v>6991318</v>
+        <v>6991255</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113745</v>
+        <v>125113787</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2704,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2728,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454575</v>
+        <v>454637</v>
       </c>
       <c r="R21" t="n">
-        <v>6991102</v>
+        <v>6991264</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2764,11 +2779,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113736</v>
+        <v>125113741</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2835,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454612</v>
+        <v>454605</v>
       </c>
       <c r="R22" t="n">
-        <v>6991255</v>
+        <v>6991152</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2902,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113743</v>
+        <v>125113739</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2942,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454601</v>
+        <v>454621</v>
       </c>
       <c r="R23" t="n">
-        <v>6991125</v>
+        <v>6991148</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2992,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3009,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113738</v>
+        <v>125113783</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3025,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454619</v>
+        <v>454548</v>
       </c>
       <c r="R24" t="n">
-        <v>6991149</v>
+        <v>6991137</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,11 +3095,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113779</v>
+        <v>125113789</v>
       </c>
       <c r="B25" t="n">
-        <v>79892</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,21 +3137,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454550</v>
+        <v>454622</v>
       </c>
       <c r="R25" t="n">
-        <v>6991138</v>
+        <v>6991320</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3218,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113761</v>
+        <v>125113793</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3258,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454762</v>
+        <v>454627</v>
       </c>
       <c r="R26" t="n">
-        <v>6991205</v>
+        <v>6991135</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3303,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3325,7 +3330,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113734</v>
+        <v>125113738</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3365,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454580</v>
+        <v>454619</v>
       </c>
       <c r="R27" t="n">
-        <v>6991256</v>
+        <v>6991149</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,7 +3410,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3432,7 +3437,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125113731</v>
+        <v>125113766</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3472,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454544</v>
+        <v>454646</v>
       </c>
       <c r="R28" t="n">
-        <v>6991123</v>
+        <v>6991263</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3539,7 +3544,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125113732</v>
+        <v>125113769</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3579,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454544</v>
+        <v>454641</v>
       </c>
       <c r="R29" t="n">
-        <v>6991166</v>
+        <v>6991336</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3646,7 +3651,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125113770</v>
+        <v>125113763</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3686,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454639</v>
+        <v>454720</v>
       </c>
       <c r="R30" t="n">
-        <v>6991344</v>
+        <v>6991164</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3726,7 +3731,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3753,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125113774</v>
+        <v>125113788</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3769,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3793,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454593</v>
+        <v>454659</v>
       </c>
       <c r="R31" t="n">
-        <v>6991337</v>
+        <v>6991284</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3829,11 +3834,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3860,7 +3860,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125113771</v>
+        <v>125113745</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454604</v>
+        <v>454575</v>
       </c>
       <c r="R32" t="n">
-        <v>6991338</v>
+        <v>6991102</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,7 +3967,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125113773</v>
+        <v>125113761</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454593</v>
+        <v>454762</v>
       </c>
       <c r="R33" t="n">
-        <v>6991340</v>
+        <v>6991205</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -2912,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113739</v>
+        <v>125113783</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,21 +2928,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454621</v>
+        <v>454548</v>
       </c>
       <c r="R23" t="n">
-        <v>6991148</v>
+        <v>6991137</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,11 +2988,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113783</v>
+        <v>125113789</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3035,21 +3030,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454548</v>
+        <v>454622</v>
       </c>
       <c r="R24" t="n">
-        <v>6991137</v>
+        <v>6991320</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113789</v>
+        <v>125113739</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454622</v>
+        <v>454621</v>
       </c>
       <c r="R25" t="n">
-        <v>6991320</v>
+        <v>6991148</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3197,6 +3192,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113734</v>
+        <v>125113771</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454580</v>
+        <v>454604</v>
       </c>
       <c r="R2" t="n">
-        <v>6991256</v>
+        <v>6991338</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113743</v>
+        <v>125113734</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454601</v>
+        <v>454580</v>
       </c>
       <c r="R3" t="n">
-        <v>6991125</v>
+        <v>6991256</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113764</v>
+        <v>125113743</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454623</v>
+        <v>454601</v>
       </c>
       <c r="R4" t="n">
-        <v>6991163</v>
+        <v>6991125</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113737</v>
+        <v>125113764</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454585</v>
+        <v>454623</v>
       </c>
       <c r="R5" t="n">
-        <v>6991218</v>
+        <v>6991163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113771</v>
+        <v>125113737</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454604</v>
+        <v>454585</v>
       </c>
       <c r="R6" t="n">
-        <v>6991338</v>
+        <v>6991218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2382,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113791</v>
+        <v>125113768</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454558</v>
+        <v>454639</v>
       </c>
       <c r="R18" t="n">
-        <v>6991102</v>
+        <v>6991313</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113768</v>
+        <v>125113736</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454639</v>
+        <v>454612</v>
       </c>
       <c r="R19" t="n">
-        <v>6991313</v>
+        <v>6991255</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113736</v>
+        <v>125113791</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2612,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454612</v>
+        <v>454558</v>
       </c>
       <c r="R20" t="n">
-        <v>6991255</v>
+        <v>6991102</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2912,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113783</v>
+        <v>125113739</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,21 +2928,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454548</v>
+        <v>454621</v>
       </c>
       <c r="R23" t="n">
-        <v>6991137</v>
+        <v>6991148</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,6 +2988,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113789</v>
+        <v>125113783</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454622</v>
+        <v>454548</v>
       </c>
       <c r="R24" t="n">
-        <v>6991320</v>
+        <v>6991137</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3116,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113739</v>
+        <v>125113789</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,21 +3137,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454621</v>
+        <v>454622</v>
       </c>
       <c r="R25" t="n">
-        <v>6991148</v>
+        <v>6991320</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,11 +3197,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113771</v>
+        <v>125113739</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454604</v>
+        <v>454621</v>
       </c>
       <c r="R2" t="n">
-        <v>6991338</v>
+        <v>6991148</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113734</v>
+        <v>125113768</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454580</v>
+        <v>454639</v>
       </c>
       <c r="R3" t="n">
-        <v>6991256</v>
+        <v>6991313</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113743</v>
+        <v>125113771</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454601</v>
+        <v>454604</v>
       </c>
       <c r="R4" t="n">
-        <v>6991125</v>
+        <v>6991338</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113764</v>
+        <v>125113774</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454623</v>
+        <v>454593</v>
       </c>
       <c r="R5" t="n">
-        <v>6991163</v>
+        <v>6991337</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113737</v>
+        <v>125113736</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454585</v>
+        <v>454612</v>
       </c>
       <c r="R6" t="n">
-        <v>6991218</v>
+        <v>6991255</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113779</v>
+        <v>125113731</v>
       </c>
       <c r="B7" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454550</v>
+        <v>454544</v>
       </c>
       <c r="R7" t="n">
-        <v>6991138</v>
+        <v>6991123</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113770</v>
+        <v>125113743</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454639</v>
+        <v>454601</v>
       </c>
       <c r="R8" t="n">
-        <v>6991344</v>
+        <v>6991125</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113774</v>
+        <v>125113733</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454593</v>
+        <v>454545</v>
       </c>
       <c r="R9" t="n">
-        <v>6991337</v>
+        <v>6991197</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113732</v>
+        <v>125113735</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1566,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454544</v>
+        <v>454573</v>
       </c>
       <c r="R10" t="n">
-        <v>6991166</v>
+        <v>6991262</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113731</v>
+        <v>125113767</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1673,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454544</v>
+        <v>454642</v>
       </c>
       <c r="R11" t="n">
-        <v>6991123</v>
+        <v>6991318</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113772</v>
+        <v>125113788</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454591</v>
+        <v>454659</v>
       </c>
       <c r="R12" t="n">
-        <v>6991345</v>
+        <v>6991284</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,11 +1821,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113733</v>
+        <v>125113745</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454545</v>
+        <v>454575</v>
       </c>
       <c r="R13" t="n">
-        <v>6991197</v>
+        <v>6991102</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113773</v>
+        <v>125113783</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454593</v>
+        <v>454548</v>
       </c>
       <c r="R14" t="n">
-        <v>6991340</v>
+        <v>6991137</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,11 +2030,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113762</v>
+        <v>125113769</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454765</v>
+        <v>454641</v>
       </c>
       <c r="R15" t="n">
-        <v>6991225</v>
+        <v>6991336</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,7 +2163,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113735</v>
+        <v>125113766</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2208,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454573</v>
+        <v>454646</v>
       </c>
       <c r="R16" t="n">
-        <v>6991262</v>
+        <v>6991263</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113767</v>
+        <v>125113779</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454642</v>
+        <v>454550</v>
       </c>
       <c r="R17" t="n">
-        <v>6991318</v>
+        <v>6991138</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,11 +2346,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,7 +2372,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113768</v>
+        <v>125113762</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2422,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454639</v>
+        <v>454765</v>
       </c>
       <c r="R18" t="n">
-        <v>6991313</v>
+        <v>6991225</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2452,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,7 +2479,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113736</v>
+        <v>125113764</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2529,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454612</v>
+        <v>454623</v>
       </c>
       <c r="R19" t="n">
-        <v>6991255</v>
+        <v>6991163</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2596,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113791</v>
+        <v>125113763</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2612,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454558</v>
+        <v>454720</v>
       </c>
       <c r="R20" t="n">
-        <v>6991102</v>
+        <v>6991164</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2666,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2805,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113741</v>
+        <v>125113791</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454605</v>
+        <v>454558</v>
       </c>
       <c r="R22" t="n">
-        <v>6991152</v>
+        <v>6991102</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2875,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,7 +2902,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113739</v>
+        <v>125113772</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2952,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454621</v>
+        <v>454591</v>
       </c>
       <c r="R23" t="n">
-        <v>6991148</v>
+        <v>6991345</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,10 +3009,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113783</v>
+        <v>125113741</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3035,21 +3025,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454548</v>
+        <v>454605</v>
       </c>
       <c r="R24" t="n">
-        <v>6991137</v>
+        <v>6991152</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,6 +3085,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113789</v>
+        <v>125113737</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454622</v>
+        <v>454585</v>
       </c>
       <c r="R25" t="n">
-        <v>6991320</v>
+        <v>6991218</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3197,6 +3192,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113793</v>
+        <v>125113732</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3239,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454627</v>
+        <v>454544</v>
       </c>
       <c r="R26" t="n">
-        <v>6991135</v>
+        <v>6991166</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,7 +3330,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113738</v>
+        <v>125113734</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454619</v>
+        <v>454580</v>
       </c>
       <c r="R27" t="n">
-        <v>6991149</v>
+        <v>6991256</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3437,10 +3437,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125113766</v>
+        <v>125113789</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3453,21 +3453,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454646</v>
+        <v>454622</v>
       </c>
       <c r="R28" t="n">
-        <v>6991263</v>
+        <v>6991320</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3513,11 +3513,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3544,7 +3539,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125113769</v>
+        <v>125113761</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3584,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454641</v>
+        <v>454762</v>
       </c>
       <c r="R29" t="n">
-        <v>6991336</v>
+        <v>6991205</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3651,7 +3646,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125113763</v>
+        <v>125113773</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3691,10 +3686,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454720</v>
+        <v>454593</v>
       </c>
       <c r="R30" t="n">
-        <v>6991164</v>
+        <v>6991340</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,10 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125113788</v>
+        <v>125113738</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3769,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3798,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454659</v>
+        <v>454619</v>
       </c>
       <c r="R31" t="n">
-        <v>6991284</v>
+        <v>6991149</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,6 +3829,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3860,10 +3860,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125113745</v>
+        <v>125113793</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3876,21 +3876,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454575</v>
+        <v>454627</v>
       </c>
       <c r="R32" t="n">
-        <v>6991102</v>
+        <v>6991135</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,7 +3967,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125113761</v>
+        <v>125113770</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454762</v>
+        <v>454639</v>
       </c>
       <c r="R33" t="n">
-        <v>6991205</v>
+        <v>6991344</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113739</v>
+        <v>125113762</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454621</v>
+        <v>454765</v>
       </c>
       <c r="R2" t="n">
-        <v>6991148</v>
+        <v>6991225</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113768</v>
+        <v>125113734</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454639</v>
+        <v>454580</v>
       </c>
       <c r="R3" t="n">
-        <v>6991313</v>
+        <v>6991256</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113771</v>
+        <v>125113767</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454604</v>
+        <v>454642</v>
       </c>
       <c r="R4" t="n">
-        <v>6991338</v>
+        <v>6991318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113774</v>
+        <v>125113743</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454593</v>
+        <v>454601</v>
       </c>
       <c r="R5" t="n">
-        <v>6991337</v>
+        <v>6991125</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113736</v>
+        <v>125113763</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454612</v>
+        <v>454720</v>
       </c>
       <c r="R6" t="n">
-        <v>6991255</v>
+        <v>6991164</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113731</v>
+        <v>125113789</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454544</v>
+        <v>454622</v>
       </c>
       <c r="R7" t="n">
-        <v>6991123</v>
+        <v>6991320</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113743</v>
+        <v>125113787</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454601</v>
+        <v>454637</v>
       </c>
       <c r="R8" t="n">
-        <v>6991125</v>
+        <v>6991264</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113733</v>
+        <v>125113772</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1464,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454545</v>
+        <v>454591</v>
       </c>
       <c r="R9" t="n">
-        <v>6991197</v>
+        <v>6991345</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113735</v>
+        <v>125113769</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1571,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454573</v>
+        <v>454641</v>
       </c>
       <c r="R10" t="n">
-        <v>6991262</v>
+        <v>6991336</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113767</v>
+        <v>125113761</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1678,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454642</v>
+        <v>454762</v>
       </c>
       <c r="R11" t="n">
-        <v>6991318</v>
+        <v>6991205</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113788</v>
+        <v>125113774</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454659</v>
+        <v>454593</v>
       </c>
       <c r="R12" t="n">
-        <v>6991284</v>
+        <v>6991337</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,6 +1811,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113745</v>
+        <v>125113736</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454575</v>
+        <v>454612</v>
       </c>
       <c r="R13" t="n">
-        <v>6991102</v>
+        <v>6991255</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113783</v>
+        <v>125113741</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454548</v>
+        <v>454605</v>
       </c>
       <c r="R14" t="n">
-        <v>6991137</v>
+        <v>6991152</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,6 +2025,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113769</v>
+        <v>125113766</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454641</v>
+        <v>454646</v>
       </c>
       <c r="R15" t="n">
-        <v>6991336</v>
+        <v>6991263</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113766</v>
+        <v>125113779</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454646</v>
+        <v>454550</v>
       </c>
       <c r="R16" t="n">
-        <v>6991263</v>
+        <v>6991138</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,11 +2239,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113779</v>
+        <v>125113773</v>
       </c>
       <c r="B17" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454550</v>
+        <v>454593</v>
       </c>
       <c r="R17" t="n">
-        <v>6991138</v>
+        <v>6991340</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,6 +2341,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,7 +2372,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113762</v>
+        <v>125113745</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454765</v>
+        <v>454575</v>
       </c>
       <c r="R18" t="n">
-        <v>6991225</v>
+        <v>6991102</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113764</v>
+        <v>125113770</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454623</v>
+        <v>454639</v>
       </c>
       <c r="R19" t="n">
-        <v>6991163</v>
+        <v>6991344</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113763</v>
+        <v>125113768</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454720</v>
+        <v>454639</v>
       </c>
       <c r="R20" t="n">
-        <v>6991164</v>
+        <v>6991313</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113787</v>
+        <v>125113737</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,21 +2709,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454637</v>
+        <v>454585</v>
       </c>
       <c r="R21" t="n">
-        <v>6991264</v>
+        <v>6991218</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,6 +2769,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113772</v>
+        <v>125113735</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2942,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454591</v>
+        <v>454573</v>
       </c>
       <c r="R23" t="n">
-        <v>6991345</v>
+        <v>6991262</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2987,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3009,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113741</v>
+        <v>125113738</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3049,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454605</v>
+        <v>454619</v>
       </c>
       <c r="R24" t="n">
-        <v>6991152</v>
+        <v>6991149</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3094,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,7 +3121,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113737</v>
+        <v>125113771</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3156,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454585</v>
+        <v>454604</v>
       </c>
       <c r="R25" t="n">
-        <v>6991218</v>
+        <v>6991338</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3201,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,7 +3228,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113732</v>
+        <v>125113739</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3263,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454544</v>
+        <v>454621</v>
       </c>
       <c r="R26" t="n">
-        <v>6991166</v>
+        <v>6991148</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3308,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,7 +3335,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113734</v>
+        <v>125113731</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3370,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454580</v>
+        <v>454544</v>
       </c>
       <c r="R27" t="n">
-        <v>6991256</v>
+        <v>6991123</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3437,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125113789</v>
+        <v>125113733</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3453,21 +3458,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3477,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454622</v>
+        <v>454545</v>
       </c>
       <c r="R28" t="n">
-        <v>6991320</v>
+        <v>6991197</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3513,6 +3518,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3539,7 +3549,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125113761</v>
+        <v>125113732</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3579,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454762</v>
+        <v>454544</v>
       </c>
       <c r="R29" t="n">
-        <v>6991205</v>
+        <v>6991166</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3646,10 +3656,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125113773</v>
+        <v>125113783</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3662,21 +3672,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3686,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454593</v>
+        <v>454548</v>
       </c>
       <c r="R30" t="n">
-        <v>6991340</v>
+        <v>6991137</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3722,11 +3732,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3753,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125113738</v>
+        <v>125113793</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3769,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3793,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454619</v>
+        <v>454627</v>
       </c>
       <c r="R31" t="n">
-        <v>6991149</v>
+        <v>6991135</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3833,7 +3838,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3860,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125113793</v>
+        <v>125113788</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3876,21 +3881,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3900,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454627</v>
+        <v>454659</v>
       </c>
       <c r="R32" t="n">
-        <v>6991135</v>
+        <v>6991284</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3936,11 +3941,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,7 +3967,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125113770</v>
+        <v>125113764</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454639</v>
+        <v>454623</v>
       </c>
       <c r="R33" t="n">
-        <v>6991344</v>
+        <v>6991163</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113762</v>
+        <v>125113733</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454765</v>
+        <v>454545</v>
       </c>
       <c r="R2" t="n">
-        <v>6991225</v>
+        <v>6991197</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113734</v>
+        <v>125113769</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454580</v>
+        <v>454641</v>
       </c>
       <c r="R3" t="n">
-        <v>6991256</v>
+        <v>6991336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113767</v>
+        <v>125113738</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454642</v>
+        <v>454619</v>
       </c>
       <c r="R4" t="n">
-        <v>6991318</v>
+        <v>6991149</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113743</v>
+        <v>125113770</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454601</v>
+        <v>454639</v>
       </c>
       <c r="R5" t="n">
-        <v>6991125</v>
+        <v>6991344</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113763</v>
+        <v>125113737</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454720</v>
+        <v>454585</v>
       </c>
       <c r="R6" t="n">
-        <v>6991164</v>
+        <v>6991218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113789</v>
+        <v>125113731</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454622</v>
+        <v>454544</v>
       </c>
       <c r="R7" t="n">
-        <v>6991320</v>
+        <v>6991123</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113787</v>
+        <v>125113789</v>
       </c>
       <c r="B8" t="n">
         <v>91030</v>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454637</v>
+        <v>454622</v>
       </c>
       <c r="R8" t="n">
-        <v>6991264</v>
+        <v>6991320</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113772</v>
+        <v>125113783</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454591</v>
+        <v>454548</v>
       </c>
       <c r="R9" t="n">
-        <v>6991345</v>
+        <v>6991137</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113769</v>
+        <v>125113768</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454641</v>
+        <v>454639</v>
       </c>
       <c r="R10" t="n">
-        <v>6991336</v>
+        <v>6991313</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113761</v>
+        <v>125113793</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454762</v>
+        <v>454627</v>
       </c>
       <c r="R11" t="n">
-        <v>6991205</v>
+        <v>6991135</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113774</v>
+        <v>125113787</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454593</v>
+        <v>454637</v>
       </c>
       <c r="R12" t="n">
-        <v>6991337</v>
+        <v>6991264</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,11 +1811,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113736</v>
+        <v>125113771</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454612</v>
+        <v>454604</v>
       </c>
       <c r="R13" t="n">
-        <v>6991255</v>
+        <v>6991338</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1917,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113741</v>
+        <v>125113763</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1989,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454605</v>
+        <v>454720</v>
       </c>
       <c r="R14" t="n">
-        <v>6991152</v>
+        <v>6991164</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2024,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113766</v>
+        <v>125113745</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2096,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454646</v>
+        <v>454575</v>
       </c>
       <c r="R15" t="n">
-        <v>6991263</v>
+        <v>6991102</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113779</v>
+        <v>125113774</v>
       </c>
       <c r="B16" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,21 +2174,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454550</v>
+        <v>454593</v>
       </c>
       <c r="R16" t="n">
-        <v>6991138</v>
+        <v>6991337</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,6 +2234,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2372,7 +2372,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113745</v>
+        <v>125113762</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454575</v>
+        <v>454765</v>
       </c>
       <c r="R18" t="n">
-        <v>6991102</v>
+        <v>6991225</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113770</v>
+        <v>125113743</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454639</v>
+        <v>454601</v>
       </c>
       <c r="R19" t="n">
-        <v>6991344</v>
+        <v>6991125</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113768</v>
+        <v>125113764</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454639</v>
+        <v>454623</v>
       </c>
       <c r="R20" t="n">
-        <v>6991313</v>
+        <v>6991163</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,7 +2693,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113737</v>
+        <v>125113739</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454585</v>
+        <v>454621</v>
       </c>
       <c r="R21" t="n">
-        <v>6991218</v>
+        <v>6991148</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113791</v>
+        <v>125113788</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454558</v>
+        <v>454659</v>
       </c>
       <c r="R22" t="n">
-        <v>6991102</v>
+        <v>6991284</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,11 +2876,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2902,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113735</v>
+        <v>125113767</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2947,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454573</v>
+        <v>454642</v>
       </c>
       <c r="R23" t="n">
-        <v>6991262</v>
+        <v>6991318</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,7 +2982,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113738</v>
+        <v>125113761</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3054,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454619</v>
+        <v>454762</v>
       </c>
       <c r="R24" t="n">
-        <v>6991149</v>
+        <v>6991205</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,7 +3089,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,7 +3116,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113771</v>
+        <v>125113736</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3161,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454604</v>
+        <v>454612</v>
       </c>
       <c r="R25" t="n">
-        <v>6991338</v>
+        <v>6991255</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,7 +3196,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,7 +3223,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113739</v>
+        <v>125113734</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3268,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454621</v>
+        <v>454580</v>
       </c>
       <c r="R26" t="n">
-        <v>6991148</v>
+        <v>6991256</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,7 +3303,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,7 +3330,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113731</v>
+        <v>125113741</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3375,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454544</v>
+        <v>454605</v>
       </c>
       <c r="R27" t="n">
-        <v>6991123</v>
+        <v>6991152</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3415,7 +3410,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,7 +3437,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125113733</v>
+        <v>125113735</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3482,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454545</v>
+        <v>454573</v>
       </c>
       <c r="R28" t="n">
-        <v>6991197</v>
+        <v>6991262</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3549,10 +3544,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125113732</v>
+        <v>125113791</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3565,21 +3560,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3589,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454544</v>
+        <v>454558</v>
       </c>
       <c r="R29" t="n">
-        <v>6991166</v>
+        <v>6991102</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,7 +3624,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3656,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125113783</v>
+        <v>125113766</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3672,21 +3667,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3696,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454548</v>
+        <v>454646</v>
       </c>
       <c r="R30" t="n">
-        <v>6991137</v>
+        <v>6991263</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3732,6 +3727,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125113793</v>
+        <v>125113772</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454627</v>
+        <v>454591</v>
       </c>
       <c r="R31" t="n">
-        <v>6991135</v>
+        <v>6991345</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3865,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125113788</v>
+        <v>125113779</v>
       </c>
       <c r="B32" t="n">
-        <v>91030</v>
+        <v>79892</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454659</v>
+        <v>454550</v>
       </c>
       <c r="R32" t="n">
-        <v>6991284</v>
+        <v>6991138</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3967,7 +3967,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125113764</v>
+        <v>125113732</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454623</v>
+        <v>454544</v>
       </c>
       <c r="R33" t="n">
-        <v>6991163</v>
+        <v>6991166</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113783</v>
+        <v>125113768</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454548</v>
+        <v>454639</v>
       </c>
       <c r="R9" t="n">
-        <v>6991137</v>
+        <v>6991313</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113768</v>
+        <v>125113783</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454639</v>
+        <v>454548</v>
       </c>
       <c r="R10" t="n">
-        <v>6991313</v>
+        <v>6991137</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113787</v>
+        <v>125113771</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454637</v>
+        <v>454604</v>
       </c>
       <c r="R12" t="n">
-        <v>6991264</v>
+        <v>6991338</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1811,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113771</v>
+        <v>125113763</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1877,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454604</v>
+        <v>454720</v>
       </c>
       <c r="R13" t="n">
-        <v>6991338</v>
+        <v>6991164</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113763</v>
+        <v>125113745</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1984,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454720</v>
+        <v>454575</v>
       </c>
       <c r="R14" t="n">
-        <v>6991164</v>
+        <v>6991102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113745</v>
+        <v>125113787</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454575</v>
+        <v>454637</v>
       </c>
       <c r="R15" t="n">
-        <v>6991102</v>
+        <v>6991264</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,11 +2132,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3865,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125113779</v>
+        <v>125113732</v>
       </c>
       <c r="B32" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454550</v>
+        <v>454544</v>
       </c>
       <c r="R32" t="n">
-        <v>6991138</v>
+        <v>6991166</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3941,6 +3941,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,10 +3972,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125113732</v>
+        <v>125113779</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3983,21 +3988,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4007,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454544</v>
+        <v>454550</v>
       </c>
       <c r="R33" t="n">
-        <v>6991166</v>
+        <v>6991138</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4043,11 +4048,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113733</v>
+        <v>125113764</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454545</v>
+        <v>454623</v>
       </c>
       <c r="R2" t="n">
-        <v>6991197</v>
+        <v>6991163</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113769</v>
+        <v>125113768</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454641</v>
+        <v>454639</v>
       </c>
       <c r="R3" t="n">
-        <v>6991336</v>
+        <v>6991313</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113738</v>
+        <v>125113793</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454619</v>
+        <v>454627</v>
       </c>
       <c r="R4" t="n">
-        <v>6991149</v>
+        <v>6991135</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113770</v>
+        <v>125113766</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454639</v>
+        <v>454646</v>
       </c>
       <c r="R5" t="n">
-        <v>6991344</v>
+        <v>6991263</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113737</v>
+        <v>125113787</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454585</v>
+        <v>454637</v>
       </c>
       <c r="R6" t="n">
-        <v>6991218</v>
+        <v>6991264</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113731</v>
+        <v>125113772</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454544</v>
+        <v>454591</v>
       </c>
       <c r="R7" t="n">
-        <v>6991123</v>
+        <v>6991345</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113789</v>
+        <v>125113762</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454622</v>
+        <v>454765</v>
       </c>
       <c r="R8" t="n">
-        <v>6991320</v>
+        <v>6991225</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113768</v>
+        <v>125113735</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454639</v>
+        <v>454573</v>
       </c>
       <c r="R9" t="n">
-        <v>6991313</v>
+        <v>6991262</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113783</v>
+        <v>125113788</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454548</v>
+        <v>454659</v>
       </c>
       <c r="R10" t="n">
-        <v>6991137</v>
+        <v>6991284</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113793</v>
+        <v>125113779</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454627</v>
+        <v>454550</v>
       </c>
       <c r="R11" t="n">
-        <v>6991135</v>
+        <v>6991138</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113771</v>
+        <v>125113734</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1775,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454604</v>
+        <v>454580</v>
       </c>
       <c r="R12" t="n">
-        <v>6991338</v>
+        <v>6991256</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113763</v>
+        <v>125113789</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454720</v>
+        <v>454622</v>
       </c>
       <c r="R13" t="n">
-        <v>6991164</v>
+        <v>6991320</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,11 +1913,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113745</v>
+        <v>125113791</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,7 +1979,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454575</v>
+        <v>454558</v>
       </c>
       <c r="R14" t="n">
         <v>6991102</v>
@@ -2029,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113787</v>
+        <v>125113783</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454637</v>
+        <v>454548</v>
       </c>
       <c r="R15" t="n">
-        <v>6991264</v>
+        <v>6991137</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113774</v>
+        <v>125113773</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2201,7 +2191,7 @@
         <v>454593</v>
       </c>
       <c r="R16" t="n">
-        <v>6991337</v>
+        <v>6991340</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,7 +2228,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,7 +2255,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113773</v>
+        <v>125113769</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2305,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454593</v>
+        <v>454641</v>
       </c>
       <c r="R17" t="n">
-        <v>6991340</v>
+        <v>6991336</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,7 +2335,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,7 +2362,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113762</v>
+        <v>125113731</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2412,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454765</v>
+        <v>454544</v>
       </c>
       <c r="R18" t="n">
-        <v>6991225</v>
+        <v>6991123</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,7 +2442,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,7 +2469,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113743</v>
+        <v>125113763</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2519,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454601</v>
+        <v>454720</v>
       </c>
       <c r="R19" t="n">
-        <v>6991125</v>
+        <v>6991164</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,7 +2549,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,7 +2576,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113764</v>
+        <v>125113738</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2626,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454623</v>
+        <v>454619</v>
       </c>
       <c r="R20" t="n">
-        <v>6991163</v>
+        <v>6991149</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,7 +2656,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2800,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113788</v>
+        <v>125113761</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2806,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454659</v>
+        <v>454762</v>
       </c>
       <c r="R22" t="n">
-        <v>6991284</v>
+        <v>6991205</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,6 +2866,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2902,7 +2897,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113767</v>
+        <v>125113774</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2942,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454642</v>
+        <v>454593</v>
       </c>
       <c r="R23" t="n">
-        <v>6991318</v>
+        <v>6991337</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,7 +3004,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113761</v>
+        <v>125113770</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3049,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454762</v>
+        <v>454639</v>
       </c>
       <c r="R24" t="n">
-        <v>6991205</v>
+        <v>6991344</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3116,7 +3111,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113736</v>
+        <v>125113733</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3156,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454612</v>
+        <v>454545</v>
       </c>
       <c r="R25" t="n">
-        <v>6991255</v>
+        <v>6991197</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3191,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,7 +3218,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113734</v>
+        <v>125113732</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3263,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454580</v>
+        <v>454544</v>
       </c>
       <c r="R26" t="n">
-        <v>6991256</v>
+        <v>6991166</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3298,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,7 +3325,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113741</v>
+        <v>125113736</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3370,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454605</v>
+        <v>454612</v>
       </c>
       <c r="R27" t="n">
-        <v>6991152</v>
+        <v>6991255</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3437,7 +3432,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125113735</v>
+        <v>125113743</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3477,10 +3472,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454573</v>
+        <v>454601</v>
       </c>
       <c r="R28" t="n">
-        <v>6991262</v>
+        <v>6991125</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3517,7 +3512,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3544,10 +3539,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125113791</v>
+        <v>125113767</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3560,21 +3555,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3584,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454558</v>
+        <v>454642</v>
       </c>
       <c r="R29" t="n">
-        <v>6991102</v>
+        <v>6991318</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,7 +3619,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,7 +3646,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125113766</v>
+        <v>125113745</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3691,10 +3686,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454646</v>
+        <v>454575</v>
       </c>
       <c r="R30" t="n">
-        <v>6991263</v>
+        <v>6991102</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,7 +3753,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125113772</v>
+        <v>125113741</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3798,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454591</v>
+        <v>454605</v>
       </c>
       <c r="R31" t="n">
-        <v>6991345</v>
+        <v>6991152</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3833,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3865,7 +3860,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125113732</v>
+        <v>125113771</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -3905,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454544</v>
+        <v>454604</v>
       </c>
       <c r="R32" t="n">
-        <v>6991166</v>
+        <v>6991338</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3940,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3972,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125113779</v>
+        <v>125113737</v>
       </c>
       <c r="B33" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3988,21 +3983,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4012,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454550</v>
+        <v>454585</v>
       </c>
       <c r="R33" t="n">
-        <v>6991138</v>
+        <v>6991218</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4048,6 +4043,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113734</v>
+        <v>125113789</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454580</v>
+        <v>454622</v>
       </c>
       <c r="R12" t="n">
-        <v>6991256</v>
+        <v>6991320</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113789</v>
+        <v>125113734</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454622</v>
+        <v>454580</v>
       </c>
       <c r="R13" t="n">
-        <v>6991320</v>
+        <v>6991256</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113764</v>
+        <v>125113745</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454623</v>
+        <v>454575</v>
       </c>
       <c r="R2" t="n">
-        <v>6991163</v>
+        <v>6991102</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113768</v>
+        <v>125113737</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454639</v>
+        <v>454585</v>
       </c>
       <c r="R3" t="n">
-        <v>6991313</v>
+        <v>6991218</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113793</v>
+        <v>125113791</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454627</v>
+        <v>454558</v>
       </c>
       <c r="R4" t="n">
-        <v>6991135</v>
+        <v>6991102</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113766</v>
+        <v>125113732</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454646</v>
+        <v>454544</v>
       </c>
       <c r="R5" t="n">
-        <v>6991263</v>
+        <v>6991166</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113787</v>
+        <v>125113738</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454637</v>
+        <v>454619</v>
       </c>
       <c r="R6" t="n">
-        <v>6991264</v>
+        <v>6991149</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113772</v>
+        <v>125113788</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454591</v>
+        <v>454659</v>
       </c>
       <c r="R7" t="n">
-        <v>6991345</v>
+        <v>6991284</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113762</v>
+        <v>125113772</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454765</v>
+        <v>454591</v>
       </c>
       <c r="R8" t="n">
-        <v>6991225</v>
+        <v>6991345</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113735</v>
+        <v>125113733</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454573</v>
+        <v>454545</v>
       </c>
       <c r="R9" t="n">
-        <v>6991262</v>
+        <v>6991197</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113788</v>
+        <v>125113793</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454659</v>
+        <v>454627</v>
       </c>
       <c r="R10" t="n">
-        <v>6991284</v>
+        <v>6991135</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113779</v>
+        <v>125113769</v>
       </c>
       <c r="B11" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454550</v>
+        <v>454641</v>
       </c>
       <c r="R11" t="n">
-        <v>6991138</v>
+        <v>6991336</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,6 +1709,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113789</v>
+        <v>125113767</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454622</v>
+        <v>454642</v>
       </c>
       <c r="R12" t="n">
-        <v>6991320</v>
+        <v>6991318</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,6 +1816,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113734</v>
+        <v>125113766</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1872,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454580</v>
+        <v>454646</v>
       </c>
       <c r="R13" t="n">
-        <v>6991256</v>
+        <v>6991263</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1927,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113791</v>
+        <v>125113761</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454558</v>
+        <v>454762</v>
       </c>
       <c r="R14" t="n">
-        <v>6991102</v>
+        <v>6991205</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2034,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113783</v>
+        <v>125113741</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454548</v>
+        <v>454605</v>
       </c>
       <c r="R15" t="n">
-        <v>6991137</v>
+        <v>6991152</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,6 +2137,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113773</v>
+        <v>125113770</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2188,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454593</v>
+        <v>454639</v>
       </c>
       <c r="R16" t="n">
-        <v>6991340</v>
+        <v>6991344</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113769</v>
+        <v>125113735</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2295,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454641</v>
+        <v>454573</v>
       </c>
       <c r="R17" t="n">
-        <v>6991336</v>
+        <v>6991262</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,7 +2382,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113731</v>
+        <v>125113736</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2402,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454544</v>
+        <v>454612</v>
       </c>
       <c r="R18" t="n">
-        <v>6991123</v>
+        <v>6991255</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,7 +2462,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113763</v>
+        <v>125113764</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2509,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454720</v>
+        <v>454623</v>
       </c>
       <c r="R19" t="n">
-        <v>6991164</v>
+        <v>6991163</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,7 +2569,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113738</v>
+        <v>125113787</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2592,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454619</v>
+        <v>454637</v>
       </c>
       <c r="R20" t="n">
-        <v>6991149</v>
+        <v>6991264</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2652,11 +2672,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2683,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113739</v>
+        <v>125113783</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2699,21 +2714,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454621</v>
+        <v>454548</v>
       </c>
       <c r="R21" t="n">
-        <v>6991148</v>
+        <v>6991137</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,11 +2774,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113761</v>
+        <v>125113789</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2806,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454762</v>
+        <v>454622</v>
       </c>
       <c r="R22" t="n">
-        <v>6991205</v>
+        <v>6991320</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,11 +2876,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,7 +2902,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113774</v>
+        <v>125113762</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454593</v>
+        <v>454765</v>
       </c>
       <c r="R23" t="n">
-        <v>6991337</v>
+        <v>6991225</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3004,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113770</v>
+        <v>125113739</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3044,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454639</v>
+        <v>454621</v>
       </c>
       <c r="R24" t="n">
-        <v>6991344</v>
+        <v>6991148</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,7 +3089,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3111,7 +3116,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113733</v>
+        <v>125113768</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3151,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454545</v>
+        <v>454639</v>
       </c>
       <c r="R25" t="n">
-        <v>6991197</v>
+        <v>6991313</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3196,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,7 +3223,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113732</v>
+        <v>125113743</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3258,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454544</v>
+        <v>454601</v>
       </c>
       <c r="R26" t="n">
-        <v>6991166</v>
+        <v>6991125</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,7 +3330,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113736</v>
+        <v>125113763</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3365,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454612</v>
+        <v>454720</v>
       </c>
       <c r="R27" t="n">
-        <v>6991255</v>
+        <v>6991164</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,7 +3410,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3432,7 +3437,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125113743</v>
+        <v>125113734</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3472,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454601</v>
+        <v>454580</v>
       </c>
       <c r="R28" t="n">
-        <v>6991125</v>
+        <v>6991256</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3539,7 +3544,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125113767</v>
+        <v>125113771</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3579,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454642</v>
+        <v>454604</v>
       </c>
       <c r="R29" t="n">
-        <v>6991318</v>
+        <v>6991338</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,7 +3624,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3646,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125113745</v>
+        <v>125113779</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3662,21 +3667,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3686,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454575</v>
+        <v>454550</v>
       </c>
       <c r="R30" t="n">
-        <v>6991102</v>
+        <v>6991138</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3722,11 +3727,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3753,7 +3753,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125113741</v>
+        <v>125113773</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454605</v>
+        <v>454593</v>
       </c>
       <c r="R31" t="n">
-        <v>6991152</v>
+        <v>6991340</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3860,7 +3860,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125113771</v>
+        <v>125113774</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454604</v>
+        <v>454593</v>
       </c>
       <c r="R32" t="n">
-        <v>6991338</v>
+        <v>6991337</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,7 +3967,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125113737</v>
+        <v>125113731</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454585</v>
+        <v>454544</v>
       </c>
       <c r="R33" t="n">
-        <v>6991218</v>
+        <v>6991123</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113745</v>
+        <v>125113770</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454575</v>
+        <v>454639</v>
       </c>
       <c r="R2" t="n">
-        <v>6991102</v>
+        <v>6991344</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113737</v>
+        <v>125113761</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454585</v>
+        <v>454762</v>
       </c>
       <c r="R3" t="n">
-        <v>6991218</v>
+        <v>6991205</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113791</v>
+        <v>125113793</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454558</v>
+        <v>454627</v>
       </c>
       <c r="R4" t="n">
-        <v>6991102</v>
+        <v>6991135</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113732</v>
+        <v>125113783</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454544</v>
+        <v>454548</v>
       </c>
       <c r="R5" t="n">
-        <v>6991166</v>
+        <v>6991137</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113738</v>
+        <v>125113769</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454619</v>
+        <v>454641</v>
       </c>
       <c r="R6" t="n">
-        <v>6991149</v>
+        <v>6991336</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113788</v>
+        <v>125113772</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454659</v>
+        <v>454591</v>
       </c>
       <c r="R7" t="n">
-        <v>6991284</v>
+        <v>6991345</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113772</v>
+        <v>125113738</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454591</v>
+        <v>454619</v>
       </c>
       <c r="R8" t="n">
-        <v>6991345</v>
+        <v>6991149</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113733</v>
+        <v>125113762</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454545</v>
+        <v>454765</v>
       </c>
       <c r="R9" t="n">
-        <v>6991197</v>
+        <v>6991225</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113793</v>
+        <v>125113733</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454627</v>
+        <v>454545</v>
       </c>
       <c r="R10" t="n">
-        <v>6991135</v>
+        <v>6991197</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113769</v>
+        <v>125113739</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454641</v>
+        <v>454621</v>
       </c>
       <c r="R11" t="n">
-        <v>6991336</v>
+        <v>6991148</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113767</v>
+        <v>125113774</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454642</v>
+        <v>454593</v>
       </c>
       <c r="R12" t="n">
-        <v>6991318</v>
+        <v>6991337</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113766</v>
+        <v>125113743</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454646</v>
+        <v>454601</v>
       </c>
       <c r="R13" t="n">
-        <v>6991263</v>
+        <v>6991125</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113761</v>
+        <v>125113763</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454762</v>
+        <v>454720</v>
       </c>
       <c r="R14" t="n">
-        <v>6991205</v>
+        <v>6991164</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113741</v>
+        <v>125113766</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454605</v>
+        <v>454646</v>
       </c>
       <c r="R15" t="n">
-        <v>6991152</v>
+        <v>6991263</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113770</v>
+        <v>125113791</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454639</v>
+        <v>454558</v>
       </c>
       <c r="R16" t="n">
-        <v>6991344</v>
+        <v>6991102</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113735</v>
+        <v>125113788</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454573</v>
+        <v>454659</v>
       </c>
       <c r="R17" t="n">
-        <v>6991262</v>
+        <v>6991284</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,11 +2351,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113736</v>
+        <v>125113731</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2422,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454612</v>
+        <v>454544</v>
       </c>
       <c r="R18" t="n">
-        <v>6991255</v>
+        <v>6991123</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2457,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113764</v>
+        <v>125113779</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>80029</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,21 +2500,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454623</v>
+        <v>454550</v>
       </c>
       <c r="R19" t="n">
-        <v>6991163</v>
+        <v>6991138</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113787</v>
+        <v>125113732</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2612,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454637</v>
+        <v>454544</v>
       </c>
       <c r="R20" t="n">
-        <v>6991264</v>
+        <v>6991166</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2672,6 +2662,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113783</v>
+        <v>125113771</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2714,21 +2709,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2738,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454548</v>
+        <v>454604</v>
       </c>
       <c r="R21" t="n">
-        <v>6991137</v>
+        <v>6991338</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,6 +2769,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113789</v>
+        <v>125113768</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454622</v>
+        <v>454639</v>
       </c>
       <c r="R22" t="n">
-        <v>6991320</v>
+        <v>6991313</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,6 +2876,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2902,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113762</v>
+        <v>125113741</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454765</v>
+        <v>454605</v>
       </c>
       <c r="R23" t="n">
-        <v>6991225</v>
+        <v>6991152</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113739</v>
+        <v>125113735</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3049,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454621</v>
+        <v>454573</v>
       </c>
       <c r="R24" t="n">
-        <v>6991148</v>
+        <v>6991262</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3094,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113768</v>
+        <v>125113737</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3156,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454639</v>
+        <v>454585</v>
       </c>
       <c r="R25" t="n">
-        <v>6991313</v>
+        <v>6991218</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3201,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113743</v>
+        <v>125113773</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3263,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454601</v>
+        <v>454593</v>
       </c>
       <c r="R26" t="n">
-        <v>6991125</v>
+        <v>6991340</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3308,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113763</v>
+        <v>125113734</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3370,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454720</v>
+        <v>454580</v>
       </c>
       <c r="R27" t="n">
-        <v>6991164</v>
+        <v>6991256</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3415,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3437,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125113734</v>
+        <v>125113787</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3453,21 +3458,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3477,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454580</v>
+        <v>454637</v>
       </c>
       <c r="R28" t="n">
-        <v>6991256</v>
+        <v>6991264</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3513,11 +3518,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125113771</v>
+        <v>125113745</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454604</v>
+        <v>454575</v>
       </c>
       <c r="R29" t="n">
-        <v>6991338</v>
+        <v>6991102</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125113779</v>
+        <v>125113764</v>
       </c>
       <c r="B30" t="n">
-        <v>79892</v>
+        <v>57635</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454550</v>
+        <v>454623</v>
       </c>
       <c r="R30" t="n">
-        <v>6991138</v>
+        <v>6991163</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3727,6 +3727,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3753,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125113773</v>
+        <v>125113789</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3769,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3793,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454593</v>
+        <v>454622</v>
       </c>
       <c r="R31" t="n">
-        <v>6991340</v>
+        <v>6991320</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3829,11 +3834,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3860,10 +3860,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125113774</v>
+        <v>125113767</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454593</v>
+        <v>454642</v>
       </c>
       <c r="R32" t="n">
-        <v>6991337</v>
+        <v>6991318</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125113731</v>
+        <v>125113736</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454544</v>
+        <v>454612</v>
       </c>
       <c r="R33" t="n">
-        <v>6991123</v>
+        <v>6991255</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -2168,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113791</v>
+        <v>125113731</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454558</v>
+        <v>454544</v>
       </c>
       <c r="R16" t="n">
-        <v>6991102</v>
+        <v>6991123</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113788</v>
+        <v>125113791</v>
       </c>
       <c r="B17" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454659</v>
+        <v>454558</v>
       </c>
       <c r="R17" t="n">
-        <v>6991284</v>
+        <v>6991102</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,6 +2351,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113731</v>
+        <v>125113788</v>
       </c>
       <c r="B18" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454544</v>
+        <v>454659</v>
       </c>
       <c r="R18" t="n">
-        <v>6991123</v>
+        <v>6991284</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,11 +2458,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113770</v>
+        <v>125113741</v>
       </c>
       <c r="B2" t="n">
         <v>57635</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454639</v>
+        <v>454605</v>
       </c>
       <c r="R2" t="n">
-        <v>6991344</v>
+        <v>6991152</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113761</v>
+        <v>125113771</v>
       </c>
       <c r="B3" t="n">
         <v>57635</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454762</v>
+        <v>454604</v>
       </c>
       <c r="R3" t="n">
-        <v>6991205</v>
+        <v>6991338</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113793</v>
+        <v>125113779</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>80029</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454627</v>
+        <v>454550</v>
       </c>
       <c r="R4" t="n">
-        <v>6991135</v>
+        <v>6991138</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113783</v>
+        <v>125113739</v>
       </c>
       <c r="B5" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454548</v>
+        <v>454621</v>
       </c>
       <c r="R5" t="n">
-        <v>6991137</v>
+        <v>6991148</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113769</v>
+        <v>125113767</v>
       </c>
       <c r="B6" t="n">
         <v>57635</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454641</v>
+        <v>454642</v>
       </c>
       <c r="R6" t="n">
-        <v>6991336</v>
+        <v>6991318</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113738</v>
+        <v>125113736</v>
       </c>
       <c r="B8" t="n">
         <v>57635</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454619</v>
+        <v>454612</v>
       </c>
       <c r="R8" t="n">
-        <v>6991149</v>
+        <v>6991255</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113762</v>
+        <v>125113738</v>
       </c>
       <c r="B9" t="n">
         <v>57635</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454765</v>
+        <v>454619</v>
       </c>
       <c r="R9" t="n">
-        <v>6991225</v>
+        <v>6991149</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113733</v>
+        <v>125113774</v>
       </c>
       <c r="B10" t="n">
         <v>57635</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454545</v>
+        <v>454593</v>
       </c>
       <c r="R10" t="n">
-        <v>6991197</v>
+        <v>6991337</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113739</v>
+        <v>125113773</v>
       </c>
       <c r="B11" t="n">
         <v>57635</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454621</v>
+        <v>454593</v>
       </c>
       <c r="R11" t="n">
-        <v>6991148</v>
+        <v>6991340</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113774</v>
+        <v>125113783</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454593</v>
+        <v>454548</v>
       </c>
       <c r="R12" t="n">
-        <v>6991337</v>
+        <v>6991137</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,11 +1816,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113743</v>
+        <v>125113733</v>
       </c>
       <c r="B13" t="n">
         <v>57635</v>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454601</v>
+        <v>454545</v>
       </c>
       <c r="R13" t="n">
-        <v>6991125</v>
+        <v>6991197</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113763</v>
+        <v>125113766</v>
       </c>
       <c r="B14" t="n">
         <v>57635</v>
@@ -1994,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454720</v>
+        <v>454646</v>
       </c>
       <c r="R14" t="n">
-        <v>6991164</v>
+        <v>6991263</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113766</v>
+        <v>125113764</v>
       </c>
       <c r="B15" t="n">
         <v>57635</v>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454646</v>
+        <v>454623</v>
       </c>
       <c r="R15" t="n">
-        <v>6991263</v>
+        <v>6991163</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,7 +2163,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113731</v>
+        <v>125113737</v>
       </c>
       <c r="B16" t="n">
         <v>57635</v>
@@ -2208,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454544</v>
+        <v>454585</v>
       </c>
       <c r="R16" t="n">
-        <v>6991123</v>
+        <v>6991218</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113791</v>
+        <v>125113745</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,7 +2310,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454558</v>
+        <v>454575</v>
       </c>
       <c r="R17" t="n">
         <v>6991102</v>
@@ -2355,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113788</v>
+        <v>125113768</v>
       </c>
       <c r="B18" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454659</v>
+        <v>454639</v>
       </c>
       <c r="R18" t="n">
-        <v>6991284</v>
+        <v>6991313</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2458,6 +2453,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113779</v>
+        <v>125113761</v>
       </c>
       <c r="B19" t="n">
-        <v>80029</v>
+        <v>57635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,21 +2500,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454550</v>
+        <v>454762</v>
       </c>
       <c r="R19" t="n">
-        <v>6991138</v>
+        <v>6991205</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,6 +2560,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,7 +2591,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113732</v>
+        <v>125113743</v>
       </c>
       <c r="B20" t="n">
         <v>57635</v>
@@ -2626,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454544</v>
+        <v>454601</v>
       </c>
       <c r="R20" t="n">
-        <v>6991166</v>
+        <v>6991125</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113771</v>
+        <v>125113793</v>
       </c>
       <c r="B21" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,21 +2714,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454604</v>
+        <v>454627</v>
       </c>
       <c r="R21" t="n">
-        <v>6991338</v>
+        <v>6991135</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,7 +2778,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113768</v>
+        <v>125113789</v>
       </c>
       <c r="B22" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2821,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454639</v>
+        <v>454622</v>
       </c>
       <c r="R22" t="n">
-        <v>6991313</v>
+        <v>6991320</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,11 +2881,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113741</v>
+        <v>125113791</v>
       </c>
       <c r="B23" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454605</v>
+        <v>454558</v>
       </c>
       <c r="R23" t="n">
-        <v>6991152</v>
+        <v>6991102</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113735</v>
+        <v>125113770</v>
       </c>
       <c r="B24" t="n">
         <v>57635</v>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454573</v>
+        <v>454639</v>
       </c>
       <c r="R24" t="n">
-        <v>6991262</v>
+        <v>6991344</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,7 +3121,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113737</v>
+        <v>125113763</v>
       </c>
       <c r="B25" t="n">
         <v>57635</v>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454585</v>
+        <v>454720</v>
       </c>
       <c r="R25" t="n">
-        <v>6991218</v>
+        <v>6991164</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,7 +3228,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113773</v>
+        <v>125113732</v>
       </c>
       <c r="B26" t="n">
         <v>57635</v>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454593</v>
+        <v>454544</v>
       </c>
       <c r="R26" t="n">
-        <v>6991340</v>
+        <v>6991166</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,7 +3335,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113734</v>
+        <v>125113762</v>
       </c>
       <c r="B27" t="n">
         <v>57635</v>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454580</v>
+        <v>454765</v>
       </c>
       <c r="R27" t="n">
-        <v>6991256</v>
+        <v>6991225</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125113787</v>
+        <v>125113731</v>
       </c>
       <c r="B28" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3458,21 +3458,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454637</v>
+        <v>454544</v>
       </c>
       <c r="R28" t="n">
-        <v>6991264</v>
+        <v>6991123</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3518,6 +3518,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3544,7 +3549,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125113745</v>
+        <v>125113735</v>
       </c>
       <c r="B29" t="n">
         <v>57635</v>
@@ -3584,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454575</v>
+        <v>454573</v>
       </c>
       <c r="R29" t="n">
-        <v>6991102</v>
+        <v>6991262</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,7 +3629,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3656,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125113764</v>
+        <v>125113788</v>
       </c>
       <c r="B30" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3667,21 +3672,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454623</v>
+        <v>454659</v>
       </c>
       <c r="R30" t="n">
-        <v>6991163</v>
+        <v>6991284</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3727,11 +3732,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3758,7 +3758,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125113789</v>
+        <v>125113787</v>
       </c>
       <c r="B31" t="n">
         <v>91184</v>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454622</v>
+        <v>454637</v>
       </c>
       <c r="R31" t="n">
-        <v>6991320</v>
+        <v>6991264</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125113767</v>
+        <v>125113734</v>
       </c>
       <c r="B32" t="n">
         <v>57635</v>
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454642</v>
+        <v>454580</v>
       </c>
       <c r="R32" t="n">
-        <v>6991318</v>
+        <v>6991256</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,7 +3967,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125113736</v>
+        <v>125113769</v>
       </c>
       <c r="B33" t="n">
         <v>57635</v>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454612</v>
+        <v>454641</v>
       </c>
       <c r="R33" t="n">
-        <v>6991255</v>
+        <v>6991336</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113745</v>
+        <v>125113793</v>
       </c>
       <c r="B17" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454575</v>
+        <v>454627</v>
       </c>
       <c r="R17" t="n">
-        <v>6991102</v>
+        <v>6991135</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113768</v>
+        <v>125113789</v>
       </c>
       <c r="B18" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454639</v>
+        <v>454622</v>
       </c>
       <c r="R18" t="n">
-        <v>6991313</v>
+        <v>6991320</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,11 +2453,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113761</v>
+        <v>125113791</v>
       </c>
       <c r="B19" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454762</v>
+        <v>454558</v>
       </c>
       <c r="R19" t="n">
-        <v>6991205</v>
+        <v>6991102</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2559,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,7 +2586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113743</v>
+        <v>125113745</v>
       </c>
       <c r="B20" t="n">
         <v>57635</v>
@@ -2631,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454601</v>
+        <v>454575</v>
       </c>
       <c r="R20" t="n">
-        <v>6991125</v>
+        <v>6991102</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113793</v>
+        <v>125113768</v>
       </c>
       <c r="B21" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2714,21 +2709,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2738,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454627</v>
+        <v>454639</v>
       </c>
       <c r="R21" t="n">
-        <v>6991135</v>
+        <v>6991313</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2773,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113789</v>
+        <v>125113761</v>
       </c>
       <c r="B22" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454622</v>
+        <v>454762</v>
       </c>
       <c r="R22" t="n">
-        <v>6991320</v>
+        <v>6991205</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,6 +2876,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113791</v>
+        <v>125113743</v>
       </c>
       <c r="B23" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454558</v>
+        <v>454601</v>
       </c>
       <c r="R23" t="n">
-        <v>6991102</v>
+        <v>6991125</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3549,10 +3549,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125113735</v>
+        <v>125113788</v>
       </c>
       <c r="B29" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3565,21 +3565,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454573</v>
+        <v>454659</v>
       </c>
       <c r="R29" t="n">
-        <v>6991262</v>
+        <v>6991284</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3625,11 +3625,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3656,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125113788</v>
+        <v>125113735</v>
       </c>
       <c r="B30" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3672,21 +3667,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3696,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454659</v>
+        <v>454573</v>
       </c>
       <c r="R30" t="n">
-        <v>6991284</v>
+        <v>6991262</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3732,6 +3727,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113773</v>
+        <v>125113783</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454593</v>
+        <v>454548</v>
       </c>
       <c r="R11" t="n">
-        <v>6991340</v>
+        <v>6991137</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113783</v>
+        <v>125113773</v>
       </c>
       <c r="B12" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454548</v>
+        <v>454593</v>
       </c>
       <c r="R12" t="n">
-        <v>6991137</v>
+        <v>6991340</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,6 +1811,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113793</v>
+        <v>125113745</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454627</v>
+        <v>454575</v>
       </c>
       <c r="R17" t="n">
-        <v>6991135</v>
+        <v>6991102</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113789</v>
+        <v>125113768</v>
       </c>
       <c r="B18" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454622</v>
+        <v>454639</v>
       </c>
       <c r="R18" t="n">
-        <v>6991320</v>
+        <v>6991313</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,6 +2453,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113791</v>
+        <v>125113761</v>
       </c>
       <c r="B19" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,21 +2500,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454558</v>
+        <v>454762</v>
       </c>
       <c r="R19" t="n">
-        <v>6991102</v>
+        <v>6991205</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,7 +2564,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,7 +2591,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113745</v>
+        <v>125113743</v>
       </c>
       <c r="B20" t="n">
         <v>57635</v>
@@ -2626,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454575</v>
+        <v>454601</v>
       </c>
       <c r="R20" t="n">
-        <v>6991102</v>
+        <v>6991125</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113768</v>
+        <v>125113793</v>
       </c>
       <c r="B21" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,21 +2714,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454639</v>
+        <v>454627</v>
       </c>
       <c r="R21" t="n">
-        <v>6991313</v>
+        <v>6991135</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,7 +2778,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113761</v>
+        <v>125113789</v>
       </c>
       <c r="B22" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2821,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454762</v>
+        <v>454622</v>
       </c>
       <c r="R22" t="n">
-        <v>6991205</v>
+        <v>6991320</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,11 +2881,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113743</v>
+        <v>125113791</v>
       </c>
       <c r="B23" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454601</v>
+        <v>454558</v>
       </c>
       <c r="R23" t="n">
-        <v>6991125</v>
+        <v>6991102</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -1568,7 +1568,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113771</v>
+        <v>125113766</v>
       </c>
       <c r="B11" t="n">
         <v>57651</v>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454604</v>
+        <v>454646</v>
       </c>
       <c r="R11" t="n">
-        <v>6991338</v>
+        <v>6991263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,7 +1670,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113770</v>
+        <v>125113771</v>
       </c>
       <c r="B12" t="n">
         <v>57651</v>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454639</v>
+        <v>454604</v>
       </c>
       <c r="R12" t="n">
-        <v>6991344</v>
+        <v>6991338</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113766</v>
+        <v>125113770</v>
       </c>
       <c r="B13" t="n">
         <v>57651</v>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454646</v>
+        <v>454639</v>
       </c>
       <c r="R13" t="n">
-        <v>6991263</v>
+        <v>6991344</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113774</v>
+        <v>125113736</v>
       </c>
       <c r="B15" t="n">
         <v>57651</v>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454593</v>
+        <v>454612</v>
       </c>
       <c r="R15" t="n">
-        <v>6991337</v>
+        <v>6991255</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2078,7 +2078,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113736</v>
+        <v>125113774</v>
       </c>
       <c r="B16" t="n">
         <v>57651</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454612</v>
+        <v>454593</v>
       </c>
       <c r="R16" t="n">
-        <v>6991255</v>
+        <v>6991337</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2282,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113738</v>
+        <v>125113737</v>
       </c>
       <c r="B18" t="n">
         <v>57651</v>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454619</v>
+        <v>454585</v>
       </c>
       <c r="R18" t="n">
-        <v>6991149</v>
+        <v>6991218</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2384,7 +2384,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113741</v>
+        <v>125113738</v>
       </c>
       <c r="B19" t="n">
         <v>57651</v>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454605</v>
+        <v>454619</v>
       </c>
       <c r="R19" t="n">
-        <v>6991152</v>
+        <v>6991149</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2486,7 +2486,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113737</v>
+        <v>125113741</v>
       </c>
       <c r="B20" t="n">
         <v>57651</v>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454585</v>
+        <v>454605</v>
       </c>
       <c r="R20" t="n">
-        <v>6991218</v>
+        <v>6991152</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,7 +2690,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113768</v>
+        <v>125113763</v>
       </c>
       <c r="B22" t="n">
         <v>57651</v>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454639</v>
+        <v>454720</v>
       </c>
       <c r="R22" t="n">
-        <v>6991313</v>
+        <v>6991164</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2792,7 +2792,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113763</v>
+        <v>125113768</v>
       </c>
       <c r="B23" t="n">
         <v>57651</v>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454720</v>
+        <v>454639</v>
       </c>
       <c r="R23" t="n">
-        <v>6991164</v>
+        <v>6991313</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2894,7 +2894,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113732</v>
+        <v>125113733</v>
       </c>
       <c r="B24" t="n">
         <v>57651</v>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454544</v>
+        <v>454545</v>
       </c>
       <c r="R24" t="n">
-        <v>6991166</v>
+        <v>6991197</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2996,7 +2996,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113735</v>
+        <v>125113734</v>
       </c>
       <c r="B25" t="n">
         <v>57651</v>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454573</v>
+        <v>454580</v>
       </c>
       <c r="R25" t="n">
-        <v>6991262</v>
+        <v>6991256</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113734</v>
+        <v>125113735</v>
       </c>
       <c r="B26" t="n">
         <v>57651</v>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454580</v>
+        <v>454573</v>
       </c>
       <c r="R26" t="n">
-        <v>6991256</v>
+        <v>6991262</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3200,7 +3200,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113733</v>
+        <v>125113732</v>
       </c>
       <c r="B27" t="n">
         <v>57651</v>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454545</v>
+        <v>454544</v>
       </c>
       <c r="R27" t="n">
-        <v>6991197</v>
+        <v>6991166</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3404,7 +3404,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125113773</v>
+        <v>125113761</v>
       </c>
       <c r="B29" t="n">
         <v>57651</v>
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454593</v>
+        <v>454762</v>
       </c>
       <c r="R29" t="n">
-        <v>6991340</v>
+        <v>6991205</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3608,7 +3608,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125113761</v>
+        <v>125113773</v>
       </c>
       <c r="B31" t="n">
         <v>57651</v>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454762</v>
+        <v>454593</v>
       </c>
       <c r="R31" t="n">
-        <v>6991205</v>
+        <v>6991340</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -1367,7 +1367,7 @@
         <v>125113764</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>125113767</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113766</v>
+        <v>125113771</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454646</v>
+        <v>454604</v>
       </c>
       <c r="R11" t="n">
-        <v>6991263</v>
+        <v>6991338</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113771</v>
+        <v>125113770</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454604</v>
+        <v>454639</v>
       </c>
       <c r="R12" t="n">
-        <v>6991338</v>
+        <v>6991344</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1772,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113770</v>
+        <v>125113766</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454639</v>
+        <v>454646</v>
       </c>
       <c r="R13" t="n">
-        <v>6991344</v>
+        <v>6991263</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1877,7 +1877,7 @@
         <v>125113772</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113736</v>
+        <v>125113774</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454612</v>
+        <v>454593</v>
       </c>
       <c r="R15" t="n">
-        <v>6991255</v>
+        <v>6991337</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113774</v>
+        <v>125113736</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454593</v>
+        <v>454612</v>
       </c>
       <c r="R16" t="n">
-        <v>6991337</v>
+        <v>6991255</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
         <v>125113743</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,10 +2282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113737</v>
+        <v>125113738</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454585</v>
+        <v>454619</v>
       </c>
       <c r="R18" t="n">
-        <v>6991218</v>
+        <v>6991149</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113738</v>
+        <v>125113741</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454619</v>
+        <v>454605</v>
       </c>
       <c r="R19" t="n">
-        <v>6991149</v>
+        <v>6991152</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2486,10 +2486,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113741</v>
+        <v>125113737</v>
       </c>
       <c r="B20" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454605</v>
+        <v>454585</v>
       </c>
       <c r="R20" t="n">
-        <v>6991152</v>
+        <v>6991218</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
         <v>125113762</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113763</v>
+        <v>125113768</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454720</v>
+        <v>454639</v>
       </c>
       <c r="R22" t="n">
-        <v>6991164</v>
+        <v>6991313</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2792,10 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113768</v>
+        <v>125113763</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454639</v>
+        <v>454720</v>
       </c>
       <c r="R23" t="n">
-        <v>6991313</v>
+        <v>6991164</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2894,10 +2894,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113733</v>
+        <v>125113732</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454545</v>
+        <v>454544</v>
       </c>
       <c r="R24" t="n">
-        <v>6991197</v>
+        <v>6991166</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2996,10 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113734</v>
+        <v>125113735</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454580</v>
+        <v>454573</v>
       </c>
       <c r="R25" t="n">
-        <v>6991256</v>
+        <v>6991262</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3098,10 +3098,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113735</v>
+        <v>125113734</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454573</v>
+        <v>454580</v>
       </c>
       <c r="R26" t="n">
-        <v>6991262</v>
+        <v>6991256</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113732</v>
+        <v>125113733</v>
       </c>
       <c r="B27" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454544</v>
+        <v>454545</v>
       </c>
       <c r="R27" t="n">
-        <v>6991166</v>
+        <v>6991197</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3305,7 +3305,7 @@
         <v>125113769</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3404,10 +3404,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125113761</v>
+        <v>125113773</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454762</v>
+        <v>454593</v>
       </c>
       <c r="R29" t="n">
-        <v>6991205</v>
+        <v>6991340</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3509,7 +3509,7 @@
         <v>125113739</v>
       </c>
       <c r="B30" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3608,10 +3608,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125113773</v>
+        <v>125113761</v>
       </c>
       <c r="B31" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454593</v>
+        <v>454762</v>
       </c>
       <c r="R31" t="n">
-        <v>6991340</v>
+        <v>6991205</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3713,7 +3713,7 @@
         <v>125113731</v>
       </c>
       <c r="B32" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>125113745</v>
       </c>
       <c r="B33" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -1976,7 +1976,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113774</v>
+        <v>125113736</v>
       </c>
       <c r="B15" t="n">
         <v>57652</v>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454593</v>
+        <v>454612</v>
       </c>
       <c r="R15" t="n">
-        <v>6991337</v>
+        <v>6991255</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2078,7 +2078,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113736</v>
+        <v>125113774</v>
       </c>
       <c r="B16" t="n">
         <v>57652</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454612</v>
+        <v>454593</v>
       </c>
       <c r="R16" t="n">
-        <v>6991255</v>
+        <v>6991337</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -1976,7 +1976,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113736</v>
+        <v>125113774</v>
       </c>
       <c r="B15" t="n">
         <v>57652</v>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454612</v>
+        <v>454593</v>
       </c>
       <c r="R15" t="n">
-        <v>6991255</v>
+        <v>6991337</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2078,7 +2078,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113774</v>
+        <v>125113736</v>
       </c>
       <c r="B16" t="n">
         <v>57652</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454593</v>
+        <v>454612</v>
       </c>
       <c r="R16" t="n">
-        <v>6991337</v>
+        <v>6991255</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -1367,7 +1367,7 @@
         <v>125113764</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>125113767</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>125113771</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>125113770</v>
       </c>
       <c r="B12" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>125113766</v>
       </c>
       <c r="B13" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>125113772</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>125113774</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>125113736</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>125113743</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>125113738</v>
       </c>
       <c r="B18" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>125113741</v>
       </c>
       <c r="B19" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>125113737</v>
       </c>
       <c r="B20" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>125113762</v>
       </c>
       <c r="B21" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>125113768</v>
       </c>
       <c r="B22" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>125113763</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>125113732</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>125113735</v>
       </c>
       <c r="B25" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>125113734</v>
       </c>
       <c r="B26" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>125113733</v>
       </c>
       <c r="B27" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>125113769</v>
       </c>
       <c r="B28" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>125113773</v>
       </c>
       <c r="B29" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>125113739</v>
       </c>
       <c r="B30" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>125113761</v>
       </c>
       <c r="B31" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>125113731</v>
       </c>
       <c r="B32" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>125113745</v>
       </c>
       <c r="B33" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -1367,7 +1367,7 @@
         <v>125113764</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>125113767</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>125113771</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>125113770</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>125113766</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>125113772</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>125113774</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>125113736</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>125113743</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>125113738</v>
       </c>
       <c r="B18" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>125113741</v>
       </c>
       <c r="B19" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>125113737</v>
       </c>
       <c r="B20" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>125113762</v>
       </c>
       <c r="B21" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>125113768</v>
       </c>
       <c r="B22" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>125113763</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>125113732</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>125113735</v>
       </c>
       <c r="B25" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>125113734</v>
       </c>
       <c r="B26" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>125113733</v>
       </c>
       <c r="B27" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>125113769</v>
       </c>
       <c r="B28" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>125113773</v>
       </c>
       <c r="B29" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>125113739</v>
       </c>
       <c r="B30" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>125113761</v>
       </c>
       <c r="B31" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>125113731</v>
       </c>
       <c r="B32" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>125113745</v>
       </c>
       <c r="B33" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 12966-2024 artfynd.xlsx
+++ b/artfynd/A 12966-2024 artfynd.xlsx
@@ -1568,7 +1568,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113771</v>
+        <v>125113770</v>
       </c>
       <c r="B11" t="n">
         <v>57657</v>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454604</v>
+        <v>454639</v>
       </c>
       <c r="R11" t="n">
-        <v>6991338</v>
+        <v>6991344</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,7 +1670,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113770</v>
+        <v>125113771</v>
       </c>
       <c r="B12" t="n">
         <v>57657</v>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454639</v>
+        <v>454604</v>
       </c>
       <c r="R12" t="n">
-        <v>6991344</v>
+        <v>6991338</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1976,7 +1976,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113774</v>
+        <v>125113736</v>
       </c>
       <c r="B15" t="n">
         <v>57657</v>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454593</v>
+        <v>454612</v>
       </c>
       <c r="R15" t="n">
-        <v>6991337</v>
+        <v>6991255</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2078,7 +2078,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113736</v>
+        <v>125113774</v>
       </c>
       <c r="B16" t="n">
         <v>57657</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454612</v>
+        <v>454593</v>
       </c>
       <c r="R16" t="n">
-        <v>6991255</v>
+        <v>6991337</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2282,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113738</v>
+        <v>125113737</v>
       </c>
       <c r="B18" t="n">
         <v>57657</v>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454619</v>
+        <v>454585</v>
       </c>
       <c r="R18" t="n">
-        <v>6991149</v>
+        <v>6991218</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2384,7 +2384,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113741</v>
+        <v>125113738</v>
       </c>
       <c r="B19" t="n">
         <v>57657</v>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454605</v>
+        <v>454619</v>
       </c>
       <c r="R19" t="n">
-        <v>6991152</v>
+        <v>6991149</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2486,7 +2486,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113737</v>
+        <v>125113741</v>
       </c>
       <c r="B20" t="n">
         <v>57657</v>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454585</v>
+        <v>454605</v>
       </c>
       <c r="R20" t="n">
-        <v>6991218</v>
+        <v>6991152</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113762</v>
+        <v>125113768</v>
       </c>
       <c r="B21" t="n">
         <v>57657</v>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454765</v>
+        <v>454639</v>
       </c>
       <c r="R21" t="n">
-        <v>6991225</v>
+        <v>6991313</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2690,7 +2690,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113768</v>
+        <v>125113762</v>
       </c>
       <c r="B22" t="n">
         <v>57657</v>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454639</v>
+        <v>454765</v>
       </c>
       <c r="R22" t="n">
-        <v>6991313</v>
+        <v>6991225</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2894,7 +2894,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113732</v>
+        <v>125113733</v>
       </c>
       <c r="B24" t="n">
         <v>57657</v>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454544</v>
+        <v>454545</v>
       </c>
       <c r="R24" t="n">
-        <v>6991166</v>
+        <v>6991197</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2996,7 +2996,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113735</v>
+        <v>125113734</v>
       </c>
       <c r="B25" t="n">
         <v>57657</v>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454573</v>
+        <v>454580</v>
       </c>
       <c r="R25" t="n">
-        <v>6991262</v>
+        <v>6991256</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113734</v>
+        <v>125113735</v>
       </c>
       <c r="B26" t="n">
         <v>57657</v>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454580</v>
+        <v>454573</v>
       </c>
       <c r="R26" t="n">
-        <v>6991256</v>
+        <v>6991262</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3200,7 +3200,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113733</v>
+        <v>125113732</v>
       </c>
       <c r="B27" t="n">
         <v>57657</v>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454545</v>
+        <v>454544</v>
       </c>
       <c r="R27" t="n">
-        <v>6991197</v>
+        <v>6991166</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3404,7 +3404,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125113773</v>
+        <v>125113761</v>
       </c>
       <c r="B29" t="n">
         <v>57657</v>
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454593</v>
+        <v>454762</v>
       </c>
       <c r="R29" t="n">
-        <v>6991340</v>
+        <v>6991205</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3608,7 +3608,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125113761</v>
+        <v>125113773</v>
       </c>
       <c r="B31" t="n">
         <v>57657</v>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454762</v>
+        <v>454593</v>
       </c>
       <c r="R31" t="n">
-        <v>6991205</v>
+        <v>6991340</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
